--- a/FLORES DE ESTRADA/Octubre/RESUMEN-Octubre-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Octubre/RESUMEN-Octubre-ESTRADA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Septiembre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9612EC0D-6315-433F-B68A-610458AB4B4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D6CAD0-7A62-4B9D-A0B3-ADCBFFD975F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$55</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Hoja1!$A$1:$H$53</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="43">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -135,34 +135,28 @@
     <t>SUELDO SRA. FERNANDA</t>
   </si>
   <si>
-    <t>AUMENTARON LOS HONORARIOS EN JULI 2025</t>
-  </si>
-  <si>
     <t>Articulos de limpieza</t>
   </si>
   <si>
-    <t xml:space="preserve">Cerrajeria CITTA </t>
-  </si>
-  <si>
-    <t>PERIODO: SEPTIEMBRE - Vto. 15/10</t>
-  </si>
-  <si>
-    <t>AYSA - SEPTIEMBRE 2025</t>
-  </si>
-  <si>
-    <t>ASCENSORES Premec S.R.L. - Mantenimiento de Ascensor SEPTIEMBRE</t>
-  </si>
-  <si>
-    <t>Administraciòn SEPTIEMBRE 2025:</t>
-  </si>
-  <si>
-    <t>Egresos gastos del mes - SEPTIEMBRE ORDINARIO</t>
-  </si>
-  <si>
-    <t>Egresos gastos del mes - SEPTIEMBRE EXTRAORDINARIO</t>
-  </si>
-  <si>
-    <t>Alterini Guido -Jardineria</t>
+    <t>PERIODO: OCTUBRE - Vto. 14/11</t>
+  </si>
+  <si>
+    <t>AYSA - OCTUBRE 2025</t>
+  </si>
+  <si>
+    <t>ASCENSORES Premec S.R.L. - Mantenimiento de Ascensor OCTUBRE</t>
+  </si>
+  <si>
+    <t>Administraciòn OCTUBRE 2025:</t>
+  </si>
+  <si>
+    <t>Egresos gastos del mes - OCTUBRE ORDINARIO</t>
+  </si>
+  <si>
+    <t>Egresos gastos del mes - OCTUBRE EXTRAORDINARIO</t>
+  </si>
+  <si>
+    <t>AUMENTARON LOS HONORARIOS EN 0ct 2025</t>
   </si>
 </sst>
 </file>
@@ -457,7 +451,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -516,7 +510,6 @@
     </xf>
     <xf numFmtId="44" fontId="5" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="11" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -548,12 +541,7 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
@@ -892,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:K52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="7" max="7" width="11.7109375" customWidth="1"/>
@@ -983,7 +971,7 @@
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
       <c r="E7" s="30" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" s="30"/>
       <c r="G7" s="31"/>
@@ -1038,16 +1026,16 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="56" t="s">
+      <c r="A12" s="55" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
@@ -1060,17 +1048,18 @@
       <c r="F13" s="36"/>
       <c r="G13" s="36"/>
       <c r="H13" s="37">
-        <v>218000</v>
+        <f>218000+218000*10%</f>
+        <v>239800</v>
       </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="57"/>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
       <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1085,24 +1074,24 @@
       <c r="G15" s="38"/>
       <c r="H15" s="39">
         <f>SUM(H13:H14)</f>
-        <v>218000</v>
+        <v>239800</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
+      <c r="B16" s="55"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
@@ -1111,7 +1100,7 @@
       <c r="F17" s="36"/>
       <c r="G17" s="36"/>
       <c r="H17" s="43">
-        <v>29691.4</v>
+        <v>29978.35</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1126,20 +1115,20 @@
       <c r="G18" s="38"/>
       <c r="H18" s="40">
         <f>SUM(H17:H17)</f>
-        <v>29691.4</v>
+        <v>29978.35</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="56"/>
-      <c r="H19" s="56"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="55"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+      <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
@@ -1166,7 +1155,7 @@
       <c r="F21" s="36"/>
       <c r="G21" s="36"/>
       <c r="H21" s="43">
-        <v>0</v>
+        <v>1809248</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1181,286 +1170,282 @@
       <c r="G22" s="36"/>
       <c r="H22" s="44">
         <f>SUM(H20:H21)</f>
-        <v>0</v>
+        <v>1809248</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="56" t="s">
+      <c r="A23" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="56"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="55"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="55"/>
+      <c r="H23" s="55"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
+      <c r="A24" s="57" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
       <c r="H24" s="43">
         <v>70000</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="60" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25" s="61"/>
-      <c r="C25" s="61"/>
-      <c r="D25" s="61"/>
-      <c r="E25" s="61"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
+      <c r="A25" s="49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
       <c r="H25" s="43">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="43">
-        <v>5000</v>
+        <v>74600</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="38" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="38"/>
+      <c r="C26" s="38"/>
+      <c r="D26" s="38"/>
+      <c r="E26" s="38"/>
+      <c r="F26" s="38"/>
+      <c r="G26" s="38"/>
+      <c r="H26" s="40">
+        <f>SUM(H24:H25)</f>
+        <v>144600</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
-      <c r="D27" s="45"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="45"/>
-      <c r="H27" s="43">
-        <v>125200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="38"/>
-      <c r="C28" s="38"/>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="40">
-        <f>SUM(H24:H27)</f>
-        <v>280200</v>
-      </c>
+      <c r="A27" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="20"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
+      <c r="A29" s="38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="38"/>
+      <c r="C29" s="38"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="38"/>
+      <c r="F29" s="38"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="46">
+        <v>156900</v>
+      </c>
+      <c r="I29" s="20"/>
+      <c r="K29" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="36"/>
-      <c r="C30" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="D30" s="36"/>
-      <c r="E30" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="36"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="20"/>
+      <c r="A30" s="55" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="55"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="55"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="55"/>
+      <c r="H30" s="55"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="38"/>
-      <c r="C31" s="38"/>
-      <c r="D31" s="38"/>
-      <c r="E31" s="38"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="38"/>
-      <c r="H31" s="46">
-        <v>148100</v>
-      </c>
-      <c r="I31" s="20"/>
-      <c r="K31" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="56" t="s">
-        <v>23</v>
-      </c>
-      <c r="B32" s="56"/>
-      <c r="C32" s="56"/>
-      <c r="D32" s="56"/>
-      <c r="E32" s="56"/>
-      <c r="F32" s="56"/>
-      <c r="G32" s="56"/>
-      <c r="H32" s="56"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="36" t="s">
+      <c r="A31" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="36"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="36"/>
-      <c r="E33" s="36"/>
-      <c r="F33" s="36"/>
-      <c r="G33" s="36"/>
-      <c r="H33" s="62">
+      <c r="B31" s="36"/>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
+      <c r="E31" s="36"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
+      <c r="H31" s="60">
         <v>99656</v>
       </c>
     </row>
+    <row r="32" spans="1:11" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="59">
+        <f>H31+H29+H26+H22+H18+H15</f>
+        <v>2480182.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="21"/>
+      <c r="J33" s="21"/>
+    </row>
     <row r="34" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="B34" s="47"/>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47"/>
-      <c r="E34" s="47"/>
-      <c r="F34" s="47"/>
-      <c r="G34" s="47"/>
-      <c r="H34" s="48">
-        <f>H33+H31+H28+H22+H18+H15</f>
-        <v>775647.4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35">
-        <f>1400000-775647.4</f>
-        <v>624352.6</v>
-      </c>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21"/>
-    </row>
-    <row r="36" spans="1:10" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="34" t="s">
+      <c r="A34" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35">
-        <f>H34+H35</f>
-        <v>1400000</v>
-      </c>
-      <c r="I36" s="23"/>
-    </row>
-    <row r="37" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="59" t="str">
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="35">
+        <f>H32+H33</f>
+        <v>2480182.35</v>
+      </c>
+      <c r="I34" s="23"/>
+    </row>
+    <row r="35" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="58" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B37" s="59"/>
-      <c r="C37" s="59"/>
-      <c r="D37" s="59"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
-      <c r="G37" s="59"/>
-      <c r="H37" s="33"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="33"/>
+    </row>
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="51"/>
+      <c r="C36" s="51"/>
+      <c r="D36" s="51"/>
+      <c r="E36" s="51"/>
+      <c r="F36" s="51"/>
+      <c r="G36" s="51"/>
+      <c r="H36" s="51"/>
+    </row>
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="51"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51"/>
+      <c r="E37" s="51"/>
+      <c r="F37" s="51"/>
+      <c r="G37" s="51"/>
+      <c r="H37" s="51"/>
     </row>
     <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="52" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="52"/>
-      <c r="E38" s="52"/>
-      <c r="F38" s="52"/>
-      <c r="G38" s="52"/>
-      <c r="H38" s="52"/>
-    </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="52"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-    </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-    </row>
-    <row r="41" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A41" s="53"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="54"/>
-      <c r="E41" s="54"/>
-      <c r="F41" s="54"/>
-      <c r="G41" s="54"/>
-      <c r="H41" s="55"/>
-      <c r="J41" s="2"/>
-    </row>
-    <row r="42" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A42" s="9" t="s">
+      <c r="B39" s="53"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="53"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="54"/>
+      <c r="J39" s="2"/>
+    </row>
+    <row r="40" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A40" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B42" s="10"/>
-      <c r="C42" s="10"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="10"/>
-      <c r="F42" s="10"/>
-      <c r="G42" s="10"/>
-      <c r="H42" s="16">
-        <v>4128514.453567781</v>
-      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="10"/>
+      <c r="H40" s="16">
+        <v>5785797.8540805168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="18">
+        <v>2432930.8005127362</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B43" s="12"/>
       <c r="C43" s="12"/>
@@ -1468,13 +1453,14 @@
       <c r="E43" s="12"/>
       <c r="F43" s="12"/>
       <c r="G43" s="12"/>
-      <c r="H43" s="18">
-        <v>2432930.8005127362</v>
+      <c r="H43" s="13">
+        <f>-( H32 )</f>
+        <v>-2480182.35</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B44" s="12"/>
       <c r="C44" s="12"/>
@@ -1482,139 +1468,109 @@
       <c r="E44" s="12"/>
       <c r="F44" s="12"/>
       <c r="G44" s="12"/>
-      <c r="H44" s="49">
-        <v>0</v>
-      </c>
-      <c r="I44" s="19"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="13">
-        <f>-( H34 )</f>
-        <v>-775647.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="13"/>
-    </row>
-    <row r="47" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+      <c r="H44" s="13"/>
+    </row>
+    <row r="45" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="17">
-        <f>SUM(H42:H46)</f>
-        <v>5785797.8540805168</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="15"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="17">
+        <f>SUM(H40:H44)</f>
+        <v>5738546.3045932539</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="8"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="8"/>
+      <c r="B47" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C47" s="50"/>
+      <c r="D47" s="50"/>
+      <c r="E47" s="50"/>
+      <c r="F47" s="50"/>
+      <c r="G47" s="50"/>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
+      <c r="B48" s="50"/>
+      <c r="C48" s="50"/>
+      <c r="D48" s="50"/>
+      <c r="E48" s="50"/>
+      <c r="F48" s="50"/>
+      <c r="G48" s="50"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
+      <c r="B49" s="50"/>
+      <c r="C49" s="50"/>
+      <c r="D49" s="50"/>
+      <c r="E49" s="50"/>
+      <c r="F49" s="50"/>
+      <c r="G49" s="50"/>
       <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="51"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
+      <c r="B50" s="50"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="50"/>
+      <c r="F50" s="50"/>
+      <c r="G50" s="50"/>
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="51"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="51"/>
-      <c r="G51" s="51"/>
+      <c r="B51" s="50"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="50"/>
+      <c r="E51" s="50"/>
+      <c r="F51" s="50"/>
+      <c r="G51" s="50"/>
       <c r="H51" s="8"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
-      <c r="B52" s="51"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="51"/>
-      <c r="G52" s="51"/>
+      <c r="B52" s="50"/>
+      <c r="C52" s="50"/>
+      <c r="D52" s="50"/>
+      <c r="E52" s="50"/>
+      <c r="F52" s="50"/>
+      <c r="G52" s="50"/>
       <c r="H52" s="8"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="8"/>
-      <c r="B53" s="51"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="51"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="8"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="8"/>
-      <c r="B54" s="51"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="51"/>
-      <c r="G54" s="51"/>
-      <c r="H54" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="B49:G54"/>
-    <mergeCell ref="A38:H39"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="B47:G52"/>
+    <mergeCell ref="A36:H37"/>
+    <mergeCell ref="A39:H39"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A35:G35"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>

--- a/FLORES DE ESTRADA/Octubre/RESUMEN-Octubre-ESTRADA.xlsx
+++ b/FLORES DE ESTRADA/Octubre/RESUMEN-Octubre-ESTRADA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\FLORES DE ESTRADA\Octubre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33D6CAD0-7A62-4B9D-A0B3-ADCBFFD975F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D3036E7-7AA3-4BEE-BF59-D609DE81535D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,6 +514,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -541,8 +543,6 @@
     <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1026,16 +1026,16 @@
       <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="57" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
     </row>
     <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36" t="s">
@@ -1053,13 +1053,13 @@
       </c>
     </row>
     <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="56"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="56"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
       <c r="H14" s="37"/>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1078,16 +1078,16 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="55"/>
-      <c r="E16" s="55"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="55"/>
-      <c r="H16" s="55"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="36" t="s">
@@ -1119,16 +1119,16 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="55" t="s">
+      <c r="A19" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
@@ -1174,27 +1174,27 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="55"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="55"/>
-      <c r="H23" s="55"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="59" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="57"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="57"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
       <c r="H24" s="43">
         <v>70000</v>
       </c>
@@ -1229,16 +1229,16 @@
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
@@ -1276,16 +1276,16 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="55" t="s">
+      <c r="A30" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="B30" s="55"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="36" t="s">
@@ -1297,7 +1297,7 @@
       <c r="E31" s="36"/>
       <c r="F31" s="36"/>
       <c r="G31" s="36"/>
-      <c r="H31" s="60">
+      <c r="H31" s="51">
         <v>99656</v>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       <c r="E32" s="47"/>
       <c r="F32" s="47"/>
       <c r="G32" s="47"/>
-      <c r="H32" s="59">
+      <c r="H32" s="50">
         <f>H31+H29+H26+H22+H18+H15</f>
         <v>2480182.35</v>
       </c>
@@ -1347,39 +1347,39 @@
       <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:10" s="1" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="58" t="str">
+      <c r="A35" s="60" t="str">
         <f>UPPER("Prevision Extraordinaria")</f>
         <v>PREVISION EXTRAORDINARIA</v>
       </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
       <c r="H35" s="33"/>
     </row>
     <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="51" t="s">
+      <c r="A36" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="51"/>
-      <c r="D36" s="51"/>
-      <c r="E36" s="51"/>
-      <c r="F36" s="51"/>
-      <c r="G36" s="51"/>
-      <c r="H36" s="51"/>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="53"/>
     </row>
     <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="51"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51"/>
-      <c r="E37" s="51"/>
-      <c r="F37" s="51"/>
-      <c r="G37" s="51"/>
-      <c r="H37" s="51"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
     </row>
     <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8"/>
@@ -1392,14 +1392,14 @@
       <c r="H38" s="8"/>
     </row>
     <row r="39" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A39" s="52"/>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="54"/>
+      <c r="A39" s="54"/>
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="55"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="56"/>
       <c r="J39" s="2"/>
     </row>
     <row r="40" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
@@ -1427,7 +1427,7 @@
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
       <c r="H41" s="18">
-        <v>2432930.8005127362</v>
+        <v>1078339</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -1482,7 +1482,7 @@
       <c r="G45" s="15"/>
       <c r="H45" s="17">
         <f>SUM(H40:H44)</f>
-        <v>5738546.3045932539</v>
+        <v>4383954.5040805172</v>
       </c>
     </row>
     <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
@@ -1497,64 +1497,64 @@
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="8"/>
-      <c r="B47" s="50" t="s">
+      <c r="B47" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="C47" s="50"/>
-      <c r="D47" s="50"/>
-      <c r="E47" s="50"/>
-      <c r="F47" s="50"/>
-      <c r="G47" s="50"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
+      <c r="F47" s="52"/>
+      <c r="G47" s="52"/>
       <c r="H47" s="8"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="8"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50"/>
-      <c r="D48" s="50"/>
-      <c r="E48" s="50"/>
-      <c r="F48" s="50"/>
-      <c r="G48" s="50"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
+      <c r="F48" s="52"/>
+      <c r="G48" s="52"/>
       <c r="H48" s="8"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="8"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
-      <c r="D49" s="50"/>
-      <c r="E49" s="50"/>
-      <c r="F49" s="50"/>
-      <c r="G49" s="50"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
       <c r="H49" s="8"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="50"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="50"/>
-      <c r="F50" s="50"/>
-      <c r="G50" s="50"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
+      <c r="D50" s="52"/>
+      <c r="E50" s="52"/>
+      <c r="F50" s="52"/>
+      <c r="G50" s="52"/>
       <c r="H50" s="8"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
-      <c r="D51" s="50"/>
-      <c r="E51" s="50"/>
-      <c r="F51" s="50"/>
-      <c r="G51" s="50"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
       <c r="H51" s="8"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50"/>
-      <c r="D52" s="50"/>
-      <c r="E52" s="50"/>
-      <c r="F52" s="50"/>
-      <c r="G52" s="50"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
+      <c r="D52" s="52"/>
+      <c r="E52" s="52"/>
+      <c r="F52" s="52"/>
+      <c r="G52" s="52"/>
       <c r="H52" s="8"/>
     </row>
   </sheetData>
